--- a/research/traditional_assets/database/data/south_africa/south_africa_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_semiconductor.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.07826923076923076</v>
+        <v>-0.8274111675126903</v>
       </c>
       <c r="H2">
-        <v>0.07826923076923076</v>
+        <v>-0.8274111675126903</v>
       </c>
       <c r="I2">
-        <v>0.347739370173031</v>
+        <v>-1.522842639593909</v>
       </c>
       <c r="J2">
-        <v>0.347739370173031</v>
+        <v>-1.522842639593909</v>
       </c>
       <c r="K2">
-        <v>-0.156</v>
+        <v>-3.04</v>
       </c>
       <c r="L2">
-        <v>0.015</v>
+        <v>-1.543147208121827</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.409</v>
+        <v>0.774</v>
       </c>
       <c r="V2">
-        <v>0.04479737130339539</v>
+        <v>0.2276470588235294</v>
       </c>
       <c r="W2">
-        <v>-0.0375</v>
+        <v>-0.7325301204819277</v>
       </c>
       <c r="X2">
-        <v>0.1303677526560863</v>
+        <v>0.2595624552324799</v>
       </c>
       <c r="Y2">
-        <v>-0.1678677526560863</v>
+        <v>-0.9920925757144076</v>
       </c>
       <c r="Z2">
-        <v>-1.430055061785903</v>
+        <v>0.4884701214976444</v>
       </c>
       <c r="AA2">
-        <v>-0.4972864464981848</v>
+        <v>-0.74386312918423</v>
       </c>
       <c r="AB2">
-        <v>0.1229852531331643</v>
+        <v>0.2208279091269737</v>
       </c>
       <c r="AC2">
-        <v>-0.6202716996313491</v>
+        <v>-0.9646910383112037</v>
       </c>
       <c r="AD2">
-        <v>0.792</v>
+        <v>0.872</v>
       </c>
       <c r="AE2">
-        <v>0.02744724899761145</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.8194472489976115</v>
+        <v>0.872</v>
       </c>
       <c r="AG2">
-        <v>0.4104472489976115</v>
+        <v>0.09799999999999998</v>
       </c>
       <c r="AH2">
-        <v>0.08236108283102553</v>
+        <v>0.2041198501872659</v>
       </c>
       <c r="AI2">
-        <v>0.1500971090338985</v>
+        <v>0.1339066339066339</v>
       </c>
       <c r="AJ2">
-        <v>0.04302180372526414</v>
+        <v>0.02801600914808462</v>
       </c>
       <c r="AK2">
-        <v>0.08126948540628261</v>
+        <v>0.01707912164517253</v>
       </c>
       <c r="AL2">
-        <v>0.008999999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="AM2">
-        <v>-0.193</v>
+        <v>0.097</v>
       </c>
       <c r="AN2">
-        <v>-0.5776805251641138</v>
+        <v>-0.5349693251533743</v>
       </c>
       <c r="AO2">
-        <v>-404.4444444444445</v>
+        <v>-30.3030303030303</v>
       </c>
       <c r="AP2">
-        <v>-0.2993780080215985</v>
+        <v>-0.06012269938650305</v>
       </c>
       <c r="AQ2">
-        <v>18.860103626943</v>
+        <v>-30.92783505154639</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.07826923076923076</v>
+        <v>-0.8274111675126903</v>
       </c>
       <c r="H3">
-        <v>0.07826923076923076</v>
+        <v>-0.8274111675126903</v>
       </c>
       <c r="I3">
-        <v>0.347739370173031</v>
+        <v>-1.522842639593909</v>
       </c>
       <c r="J3">
-        <v>0.347739370173031</v>
+        <v>-1.522842639593909</v>
       </c>
       <c r="K3">
-        <v>-0.156</v>
+        <v>-3.04</v>
       </c>
       <c r="L3">
-        <v>0.015</v>
+        <v>-1.543147208121827</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.409</v>
+        <v>0.774</v>
       </c>
       <c r="V3">
-        <v>0.04479737130339539</v>
+        <v>0.2276470588235294</v>
       </c>
       <c r="W3">
-        <v>-0.0375</v>
+        <v>-0.7325301204819277</v>
       </c>
       <c r="X3">
-        <v>0.1303677526560863</v>
+        <v>0.2595624552324799</v>
       </c>
       <c r="Y3">
-        <v>-0.1678677526560863</v>
+        <v>-0.9920925757144076</v>
       </c>
       <c r="Z3">
-        <v>-1.430055061785903</v>
+        <v>0.4884701214976444</v>
       </c>
       <c r="AA3">
-        <v>-0.4972864464981848</v>
+        <v>-0.74386312918423</v>
       </c>
       <c r="AB3">
-        <v>0.1229852531331643</v>
+        <v>0.2208279091269737</v>
       </c>
       <c r="AC3">
-        <v>-0.6202716996313491</v>
+        <v>-0.9646910383112037</v>
       </c>
       <c r="AD3">
-        <v>0.792</v>
+        <v>0.872</v>
       </c>
       <c r="AE3">
-        <v>0.02744724899761145</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.8194472489976115</v>
+        <v>0.872</v>
       </c>
       <c r="AG3">
-        <v>0.4104472489976115</v>
+        <v>0.09799999999999998</v>
       </c>
       <c r="AH3">
-        <v>0.08236108283102553</v>
+        <v>0.2041198501872659</v>
       </c>
       <c r="AI3">
-        <v>0.1500971090338985</v>
+        <v>0.1339066339066339</v>
       </c>
       <c r="AJ3">
-        <v>0.04302180372526414</v>
+        <v>0.02801600914808462</v>
       </c>
       <c r="AK3">
-        <v>0.08126948540628261</v>
+        <v>0.01707912164517253</v>
       </c>
       <c r="AL3">
-        <v>0.008999999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="AM3">
-        <v>-0.193</v>
+        <v>0.097</v>
       </c>
       <c r="AN3">
-        <v>-0.5776805251641138</v>
+        <v>-0.5349693251533743</v>
       </c>
       <c r="AO3">
-        <v>-404.4444444444445</v>
+        <v>-30.3030303030303</v>
       </c>
       <c r="AP3">
-        <v>-0.2993780080215985</v>
+        <v>-0.06012269938650305</v>
       </c>
       <c r="AQ3">
-        <v>18.860103626943</v>
+        <v>-30.92783505154639</v>
       </c>
     </row>
   </sheetData>
